--- a/Hunts/hunt2_credential_access_proxy_auth_tracker.xlsx
+++ b/Hunts/hunt2_credential_access_proxy_auth_tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="104">
   <si>
     <t xml:space="preserve">HUNT 2: Credential Access &amp; Proxy Authentication</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <t xml:space="preserve">CURRENT_USER, TARGET_USER, DBPROXY_USERNAME, EXTERNAL_USERID, GLOBAL_USERID, AUTHENTICATION_TYPE, CLIENT ADDRESS, HOST, SESSIONID, RETURN_CODE, ACTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment Schema Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This environment ingests Oracle Audit Vault as JSON (sourcetype oracle:audit:text, index=database). Splunk auto-extracts top-level fields (USER_NAME, CLIENT_HOST_NAME, CLIENT_IP, EVENT_NAME, COMMAND_CLASS, etc.). Identity/proxy fields (DBPROXY_USERNAME, CURRENT_USER, EXTERNAL_USERID, GLOBAL_USERID, AUTHENTICATION_TYPE, SESSIONID) live inside the EXTENSION field as "Key=Value::Key=Value" pairs. Confirmed via field enumeration on 8/9/26. See each story tab's "Field Mapping Notes" section for details.</t>
   </si>
   <si>
     <t xml:space="preserve">Overarching Hypothesis</t>
@@ -186,21 +192,27 @@
     <t xml:space="preserve">Splunk Query — copy into Splunk search bar</t>
   </si>
   <si>
-    <t xml:space="preserve">index=database
-| rex field=_raw "(?i)DBPROXY_USERNAME[=:]\"?(?&lt;proxy_user&gt;[^\"]+)"
-| rex field=_raw "(?i)CURRENT_USER[=:]\"?(?&lt;db_user&gt;[^\"]+)"
-| rex field=_raw "(?i)CLIENT ADDRESS[=:]\"?(?&lt;src_ip&gt;[0-9A-Fa-f:\.]+)"
-| rex field=_raw "(?i)HOST[=:]\"?(?&lt;host&gt;[^\"]+)"
-| search proxy_user=*
-| stats count dc(db_user) AS impersonated_users values(db_user) AS users values(src_ip) AS source_ips values(host) AS hosts earliest(_time) AS first_seen latest(_time) AS last_seen by proxy_user
+    <t xml:space="preserve">index=database sourcetype=oracle:audit:text
+| rex field=EXTENSION "(?i)DBPROXY_USERNAME=(?&lt;proxy_user&gt;[^:]+)"
+| where isnotnull(proxy_user)
+| rex field=EXTENSION "(?i)CURRENT_USER=(?&lt;ext_user&gt;[^:]+)"
+| eval db_user=coalesce(ext_user, USER_NAME, user)
+| eval client_host=coalesce(CLIENT_HOST_NAME, src)
+| stats count dc(db_user) AS impersonated_users values(db_user) AS users values(CLIENT_IP) AS source_ips values(client_host) AS hosts earliest(_time) AS first_seen latest(_time) AS last_seen by proxy_user
 | convert ctime(first_seen) ctime(last_seen)
 | sort -impersonated_users</t>
   </si>
   <si>
+    <t xml:space="preserve">Field Mapping Notes (this environment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This environment feeds Oracle Audit Vault JSON into Splunk (sourcetype oracle:audit:text). Top-level fields (USER_NAME, CLIENT_HOST_NAME, CLIENT_IP, etc.) are auto-extracted by Splunk. Proxy/identity fields (DBPROXY_USERNAME, CURRENT_USER, EXTERNAL_USERID, GLOBAL_USERID, AUTHENTICATION_TYPE, SESSIONID) live inside the EXTENSION field as "Key=Value" pairs joined by "::" — confirmed present via: index=database | rex field=EXTENSION max_match=0 "(?&lt;ext_key&gt;[A-Za-z_]+)=" | stats values(ext_key) AS extension_keys. Key casing varies by record subtype (CURRENT_USER / Current_User / current_user); (?i) in rex handles that. db_user falls back to top-level USER_NAME/user when EXTENSION has no CURRENT_USER (e.g. some SYSDBA/local logons show USER_NAME="/" with the real actor only in EXTENSION).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigation Pivot Fields</t>
   </si>
   <si>
-    <t xml:space="preserve">DBPROXY_USERNAME, CURRENT_USER, CLIENT ADDRESS, HOST, SESSIONID</t>
+    <t xml:space="preserve">DBPROXY_USERNAME, CURRENT_USER, CLIENT_IP, CLIENT_HOST_NAME, SESSIONID (all inside EXTENSION unless noted)</t>
   </si>
   <si>
     <t xml:space="preserve">Operational Notes</t>
@@ -209,7 +221,8 @@
     <t xml:space="preserve">• Verify whether the proxy account belongs to an approved application.
 • Review historical proxy activity.
 • Pivot into privilege escalation and object access.
-• Review recent application configuration changes.</t>
+• Review recent application configuration changes.
+• Validate DBPROXY_USERNAME is actually populated in your data before trusting a zero-result run — confirm with: index=database | search EXTENSION="*DBPROXY_USERNAME=*" | head 5</t>
   </si>
   <si>
     <t xml:space="preserve">Expected False Positives</t>
@@ -253,18 +266,22 @@
 • Authentication from unfamiliar CLIENT ADDRESS</t>
   </si>
   <si>
-    <t xml:space="preserve">index=database
-| search "LOGON"
-| rex field=_raw "(?i)CURRENT_USER[=:]\"?(?&lt;db_user&gt;[^\"]+)"
-| rex field=_raw "(?i)EXTERNAL_USERID[=:]\"?(?&lt;external_user&gt;[^\"]+)"
-| rex field=_raw "(?i)GLOBAL_USERID[=:]\"?(?&lt;global_user&gt;[^\"]+)"
-| rex field=_raw "(?i)AUTHENTICATION_TYPE[=:]\"?(?&lt;authentication_type&gt;[^\"]+)"
-| rex field=_raw "(?i)CLIENT ADDRESS[=:]\"?(?&lt;src_ip&gt;[0-9A-Fa-f:\.]+)"
-| stats count values(external_user) AS external_identity values(global_user) AS global_identity values(authentication_type) AS authentication_types values(src_ip) AS source_ips by db_user
+    <t xml:space="preserve">index=database sourcetype=oracle:audit:text COMMAND_CLASS=LOGON
+| rex field=EXTENSION "(?i)CURRENT_USER=(?&lt;ext_user&gt;[^:]+)"
+| eval db_user=coalesce(ext_user, USER_NAME, user)
+| rex field=EXTENSION "(?i)EXTERNAL_USERID=(?&lt;external_user&gt;[^:]+)"
+| rex field=EXTENSION "(?i)GLOBAL_USERID=(?&lt;global_user&gt;[^:]+)"
+| rex field=EXTENSION "(?i)AUTHENTICATION_TYPE=(?&lt;auth_type_a&gt;[^:]+)"
+| rex field=EXTENSION "(?i)Authenticated\s+by=(?&lt;auth_type_b&gt;[^:]+)"
+| eval authentication_type=coalesce(auth_type_a, auth_type_b)
+| stats count values(external_user) AS external_identity values(global_user) AS global_identity values(authentication_type) AS authentication_types values(CLIENT_IP) AS source_ips by db_user
 | sort -count</t>
   </si>
   <si>
-    <t xml:space="preserve">CURRENT_USER, EXTERNAL_USERID, GLOBAL_USERID, AUTHENTICATION_TYPE, CLIENT ADDRESS</t>
+    <t xml:space="preserve">Same EXTENSION-field approach as 2A. AUTHENTICATION_TYPE appears under two possible key names in this environment's data — the ALL_CAPS "AUTHENTICATION_TYPE" key (some record subtypes) and the literal "Authenticated by" key with a space (seen directly in a sample LOGON event: "...TransactionId=0000000000000000::Authenticated by=DATABASE"). The query coalesces both so neither format is missed. EXTERNAL_USERID and GLOBAL_USERID are confirmed to exist as EXTENSION keys in this schema; validate they're actually populated for your logon events before relying on empty results as a negative finding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURRENT_USER, EXTERNAL_USERID, GLOBAL_USERID, AUTHENTICATION_TYPE (all inside EXTENSION), CLIENT_IP</t>
   </si>
   <si>
     <t xml:space="preserve">• Validate the identity mapping.
@@ -291,17 +308,21 @@
 • Privileged accounts using unfamiliar authentication methods</t>
   </si>
   <si>
-    <t xml:space="preserve">index=database
-| search "LOGON"
-| rex field=_raw "(?i)CURRENT_USER[=:]\"?(?&lt;db_user&gt;[^\"]+)"
-| rex field=_raw "(?i)AUTHENTICATION_TYPE[=:]\"?(?&lt;authentication_type&gt;[^\"]+)"
-| rex field=_raw "(?i)CLIENT ADDRESS[=:]\"?(?&lt;src_ip&gt;[^\"]+)"
-| stats count dc(authentication_type) AS auth_methods values(authentication_type) AS authentication_methods values(src_ip) AS source_ips by db_user
+    <t xml:space="preserve">index=database sourcetype=oracle:audit:text COMMAND_CLASS=LOGON
+| rex field=EXTENSION "(?i)CURRENT_USER=(?&lt;ext_user&gt;[^:]+)"
+| eval db_user=coalesce(ext_user, USER_NAME, user)
+| rex field=EXTENSION "(?i)AUTHENTICATION_TYPE=(?&lt;auth_type_a&gt;[^:]+)"
+| rex field=EXTENSION "(?i)Authenticated\s+by=(?&lt;auth_type_b&gt;[^:]+)"
+| eval authentication_type=coalesce(auth_type_a, auth_type_b)
+| stats count dc(authentication_type) AS auth_methods values(authentication_type) AS authentication_methods values(CLIENT_IP) AS source_ips by db_user
 | where auth_methods&gt;1
 | sort -auth_methods</t>
   </si>
   <si>
-    <t xml:space="preserve">CURRENT_USER, AUTHENTICATION_TYPE, CLIENT ADDRESS, SESSIONID</t>
+    <t xml:space="preserve">Same authentication_type coalesce logic as 2B (handles both "AUTHENTICATION_TYPE=" and "Authenticated by=" key forms found in this environment's EXTENSION field).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURRENT_USER, AUTHENTICATION_TYPE (inside EXTENSION), CLIENT_IP, SESSIONID</t>
   </si>
   <si>
     <t xml:space="preserve">• Validate approved authentication methods.
@@ -327,16 +348,19 @@
 • High authentication diversity</t>
   </si>
   <si>
-    <t xml:space="preserve">index=database
-| search "LOGON"
-| rex field=_raw "(?i)CURRENT_USER[=:]\"?(?&lt;db_user&gt;[^\"]+)"
-| rex field=_raw "(?i)EXTERNAL_USERID[=:]\"?(?&lt;external_user&gt;[^\"]+)"
-| rex field=_raw "(?i)GLOBAL_USERID[=:]\"?(?&lt;global_user&gt;[^\"]+)"
+    <t xml:space="preserve">index=database sourcetype=oracle:audit:text COMMAND_CLASS=LOGON
+| rex field=EXTENSION "(?i)CURRENT_USER=(?&lt;ext_user&gt;[^:]+)"
+| eval db_user=coalesce(ext_user, USER_NAME, user)
+| rex field=EXTENSION "(?i)EXTERNAL_USERID=(?&lt;external_user&gt;[^:]+)"
+| rex field=EXTENSION "(?i)GLOBAL_USERID=(?&lt;global_user&gt;[^:]+)"
 | stats dc(external_user) AS external_users dc(global_user) AS global_users values(external_user) AS external_identity values(global_user) AS global_identity by db_user
 | where external_users&gt;1 OR global_users&gt;1</t>
   </si>
   <si>
-    <t xml:space="preserve">CURRENT_USER, EXTERNAL_USERID, GLOBAL_USERID</t>
+    <t xml:space="preserve">Same EXTERNAL_USERID/GLOBAL_USERID EXTENSION-field extraction as 2B/2D share the same source fields; only the aggregation logic differs (this story pivots on db_user having &gt;1 distinct identity, vs. 2B which profiles every db_user regardless of count).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURRENT_USER, EXTERNAL_USERID, GLOBAL_USERID (all inside EXTENSION)</t>
   </si>
   <si>
     <t xml:space="preserve">• Validate approved identity mappings.
@@ -362,22 +386,25 @@
 • New authentication source for privileged users</t>
   </si>
   <si>
-    <t xml:space="preserve">index=database
-| search "LOGON"
-| rex field=_raw "(?i)CURRENT_USER[=:]\"?(?&lt;db_user&gt;[^\"]+)"
-| rex field=_raw "(?i)CLIENT ADDRESS[=:]\"?(?&lt;src_ip&gt;[^\"]+)"
-| rex field=_raw "(?i)HOST[=:]\"?(?&lt;host&gt;[^\"]+)"
-| stats earliest(_time) AS first_seen latest(_time) AS last_seen values(host) AS hosts by db_user src_ip
+    <t xml:space="preserve">index=database sourcetype=oracle:audit:text COMMAND_CLASS=LOGON
+| rex field=EXTENSION "(?i)CURRENT_USER=(?&lt;ext_user&gt;[^:]+)"
+| eval db_user=coalesce(ext_user, USER_NAME, user)
+| eval client_host=coalesce(CLIENT_HOST_NAME, src)
+| stats earliest(_time) AS first_seen latest(_time) AS last_seen values(CLIENT_IP) AS client_ips count by db_user client_host
 | convert ctime(first_seen) ctime(last_seen)
 | sort first_seen</t>
   </si>
   <si>
-    <t xml:space="preserve">CURRENT_USER, CLIENT ADDRESS, HOST, SESSIONID</t>
+    <t xml:space="preserve">Uses top-level CLIENT_HOST_NAME/CLIENT_IP fields (already auto-extracted by Splunk from the JSON event) rather than EXTENSION, since those were directly confirmed in sample events. IMPORTANT: this query only ranks db_user/client_host pairs by first_seen within your chosen search window — it does NOT compare against history outside that window, so everything looks equally "first seen" if the window is short. To find genuinely NEW sources: run this over a long baseline (e.g. last 90 days), then filter to combos whose first_seen falls only in the most recent few days, e.g. add: | where first_seen &gt; relative_time(now(), "-7d@d").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURRENT_USER (inside EXTENSION), CLIENT_HOST_NAME, CLIENT_IP</t>
   </si>
   <si>
     <t xml:space="preserve">• Verify the endpoint with the asset inventory.
 • Determine whether the user normally authenticates from the source.
-• Pivot into all subsequent Oracle activity from the same session.</t>
+• Pivot into all subsequent Oracle activity from the same session.
+• Run over a long lookback (90+ days) and filter to recent first_seen values — see schema notes.</t>
   </si>
   <si>
     <t xml:space="preserve">New workstations; VPN changes; Device replacement; Disaster recovery activities.</t>
@@ -390,7 +417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,6 +500,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -480,7 +514,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,7 +530,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -508,7 +542,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -561,88 +601,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -691,7 +743,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -898,250 +950,261 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="6" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="B15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="8" t="str">
         <f aca="false">'Master Tracker'!C4</f>
         <v>Not Started</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="7" t="str">
+      <c r="D16" s="8" t="str">
         <f aca="false">'Master Tracker'!C5</f>
         <v>Not Started</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="6" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="7" t="str">
+      <c r="B17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="8" t="str">
         <f aca="false">'Master Tracker'!C6</f>
         <v>Not Started</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="6" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="7" t="str">
+      <c r="D18" s="8" t="str">
         <f aca="false">'Master Tracker'!C7</f>
         <v>Not Started</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="7" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="8" t="str">
         <f aca="false">'Master Tracker'!C8</f>
         <v>Not Started</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D27"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1161,145 +1224,145 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>38</v>
       </c>
+      <c r="G3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="10"/>
+      <c r="A5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="10"/>
+      <c r="A6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
+      <c r="A7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
+      <c r="A8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>40</v>
+      <c r="A11" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>41</v>
+      <c r="A12" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>42</v>
+      <c r="A13" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1331,173 +1394,185 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>20</v>
+      <c r="A3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>45</v>
+      <c r="A4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="4"/>
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4"/>
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="15"/>
+      <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
+      <c r="A17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="16"/>
+      <c r="A18" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="3"/>
+      <c r="A20" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="3"/>
+      <c r="A23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="3"/>
+      <c r="A26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="17"/>
-    </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="19"/>
-    </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
+      <c r="A29" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B30" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="B32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="19"/>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="19"/>
+      <c r="A34" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -1513,6 +1588,8 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1529,173 +1606,185 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="17"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="B35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B36" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="17"/>
-    </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="19"/>
-    </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="19"/>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="19"/>
+      <c r="B38" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -1711,6 +1800,8 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1727,165 +1818,177 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>25</v>
+      <c r="A3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>73</v>
+      <c r="A4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="4"/>
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4"/>
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="15"/>
+      <c r="A10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="16"/>
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="135" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="3"/>
+      <c r="A18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="3"/>
+      <c r="A21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="3"/>
+      <c r="A24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
+      <c r="A27" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="20" t="s">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="B30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="19"/>
+      <c r="A32" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -1901,6 +2004,8 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1917,165 +2022,177 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>25</v>
+      <c r="A3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>81</v>
+      <c r="A4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="4"/>
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4"/>
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="15"/>
+      <c r="A10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="4"/>
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="16"/>
+      <c r="A16" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="3"/>
+      <c r="A18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="3"/>
+      <c r="A21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="3"/>
+      <c r="A24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
+      <c r="A27" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="20" t="s">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="B30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="19"/>
+      <c r="A32" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -2091,6 +2208,8 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2107,165 +2226,177 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>25</v>
+      <c r="A3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>89</v>
+      <c r="A4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="4"/>
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4"/>
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="15"/>
+      <c r="A10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="16"/>
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" s="3"/>
+      <c r="A18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="3"/>
+      <c r="A21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="3"/>
+      <c r="A24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
+      <c r="A27" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="19"/>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="20" t="s">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="B30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="19"/>
+      <c r="A32" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -2281,6 +2412,8 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
